--- a/data/trans_orig/IMC-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IMC-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IMC Adultos</t>
+          <t>IMC Adultos (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,12 +721,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,26; 27,03</t>
+          <t>26,28; 27,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,21; 27,11</t>
+          <t>26,25; 27,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,42 +736,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,28; 24,16</t>
+          <t>23,31; 24,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,45; 24,35</t>
+          <t>23,45; 24,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,29; 25,29</t>
+          <t>24,21; 25,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,24; 24,93</t>
+          <t>24,21; 24,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,94; 25,5</t>
+          <t>24,95; 25,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,23; 25,81</t>
+          <t>25,19; 25,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,5; 26,18</t>
+          <t>25,49; 26,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,24; 25,74</t>
+          <t>25,22; 25,75</t>
         </is>
       </c>
     </row>
@@ -856,32 +856,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,64; 26,3</t>
+          <t>25,63; 26,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,37; 27,09</t>
+          <t>26,38; 27,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,83; 26,65</t>
+          <t>25,83; 26,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,39; 27,11</t>
+          <t>26,39; 27,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,63; 24,47</t>
+          <t>23,64; 24,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,32; 25,29</t>
+          <t>24,35; 25,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,27 +891,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,86; 25,58</t>
+          <t>24,84; 25,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,73; 25,28</t>
+          <t>24,72; 25,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,55; 26,2</t>
+          <t>25,58; 26,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,19; 25,84</t>
+          <t>25,24; 25,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,77; 26,34</t>
+          <t>25,79; 26,34</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,29; 26,94</t>
+          <t>26,3; 26,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,93; 27,61</t>
+          <t>26,99; 27,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,45; 27,23</t>
+          <t>26,43; 27,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,17; 29,52</t>
+          <t>27,12; 29,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,76; 26,45</t>
+          <t>24,85; 26,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,45; 27,86</t>
+          <t>26,35; 27,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,47; 27,02</t>
+          <t>25,42; 26,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,92; 26,08</t>
+          <t>24,87; 26,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,04; 26,72</t>
+          <t>26,04; 26,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,94; 27,54</t>
+          <t>26,93; 27,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,36; 27,02</t>
+          <t>26,32; 27,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,69; 29,11</t>
+          <t>26,67; 29,26</t>
         </is>
       </c>
     </row>
@@ -1136,47 +1136,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,21; 26,61</t>
+          <t>26,23; 26,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,74; 27,24</t>
+          <t>26,74; 27,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,69; 27,21</t>
+          <t>26,7; 27,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,87; 27,51</t>
+          <t>26,93; 27,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,78; 25,48</t>
+          <t>24,78; 25,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,49; 26,23</t>
+          <t>25,48; 26,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,02; 25,74</t>
+          <t>25,04; 25,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,63; 30,74</t>
+          <t>25,61; 30,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,76; 26,11</t>
+          <t>25,76; 26,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,06; 26,49</t>
+          <t>26,1; 26,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,49; 29,58</t>
+          <t>26,47; 29,38</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,25; 26,11</t>
+          <t>25,26; 26,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,26; 26,95</t>
+          <t>26,28; 26,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,37; 27,11</t>
+          <t>26,36; 27,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,29; 27,27</t>
+          <t>26,32; 27,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,91; 26,71</t>
+          <t>25,9; 26,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,02; 27,87</t>
+          <t>26,99; 27,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,62; 27,39</t>
+          <t>26,6; 27,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,61; 27,39</t>
+          <t>26,7; 27,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,74; 26,42</t>
+          <t>25,77; 26,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,83; 27,37</t>
+          <t>26,8; 27,4</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26,62; 27,16</t>
+          <t>26,61; 27,17</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,67; 27,26</t>
+          <t>26,66; 27,27</t>
         </is>
       </c>
     </row>
@@ -1416,52 +1416,52 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,17; 23,81</t>
+          <t>23,18; 23,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,38; 24,26</t>
+          <t>23,4; 24,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,01; 23,93</t>
+          <t>23,02; 23,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,12; 24,92</t>
+          <t>23,15; 24,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,62; 26,15</t>
+          <t>25,65; 26,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,39; 27,05</t>
+          <t>26,38; 27,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,22; 26,92</t>
+          <t>26,25; 26,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,72; 26,42</t>
+          <t>25,74; 26,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25,2; 25,67</t>
+          <t>25,2; 25,65</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,85; 26,4</t>
+          <t>25,88; 26,44</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25,24; 25,94</t>
+          <t>25,21; 25,91</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,89; 26,15</t>
+          <t>25,89; 26,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,53; 26,82</t>
+          <t>26,52; 26,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,31; 26,62</t>
+          <t>26,33; 26,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,62; 27,75</t>
+          <t>26,62; 27,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,23; 25,55</t>
+          <t>25,21; 25,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,08; 26,42</t>
+          <t>26,09; 26,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,8; 26,17</t>
+          <t>25,8; 26,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,84; 27,93</t>
+          <t>25,84; 27,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,6; 25,8</t>
+          <t>25,59; 25,79</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,33; 26,56</t>
+          <t>26,34; 26,57</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26,11; 26,35</t>
+          <t>26,11; 26,33</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,28; 27,52</t>
+          <t>26,3; 27,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IMC-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26,27</t>
+          <t>26,24</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24,55</t>
+          <t>24,6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,89; 26,52</t>
+          <t>25,89; 26,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,28; 27,0</t>
+          <t>26,22; 26,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,25; 27,16</t>
+          <t>26,25; 27,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,93; 26,65</t>
+          <t>25,9; 26,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,31; 24,26</t>
+          <t>23,3; 24,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,45; 24,38</t>
+          <t>23,48; 24,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,21; 25,28</t>
+          <t>24,26; 25,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,21; 24,95</t>
+          <t>24,28; 24,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,95; 25,51</t>
+          <t>24,95; 25,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,19; 25,82</t>
+          <t>25,16; 25,78</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25,49; 26,18</t>
+          <t>25,49; 26,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,22; 25,75</t>
+          <t>25,24; 25,73</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26,73</t>
+          <t>26,7</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,24</t>
+          <t>25,26</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,05</t>
+          <t>26,03</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,63; 26,29</t>
+          <t>25,63; 26,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,38; 27,08</t>
+          <t>26,35; 27,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,83; 26,64</t>
+          <t>25,83; 26,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,39; 27,17</t>
+          <t>26,33; 27,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,64; 24,45</t>
+          <t>23,63; 24,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,35; 25,31</t>
+          <t>24,33; 25,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,37; 25,32</t>
+          <t>24,38; 25,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,84; 25,59</t>
+          <t>24,91; 25,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,72; 25,28</t>
+          <t>24,71; 25,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25,58; 26,17</t>
+          <t>25,55; 26,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25,24; 25,86</t>
+          <t>25,2; 25,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,79; 26,34</t>
+          <t>25,74; 26,31</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28,35</t>
+          <t>27,17</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,47</t>
+          <t>25,49</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,79</t>
+          <t>26,7</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,3; 26,94</t>
+          <t>26,28; 26,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,99; 27,65</t>
+          <t>26,98; 27,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,47 +1011,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27,12; 29,51</t>
+          <t>26,83; 27,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,85; 26,49</t>
+          <t>24,84; 26,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,35; 27,77</t>
+          <t>26,3; 27,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,42; 26,98</t>
+          <t>25,47; 26,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24,87; 26,05</t>
+          <t>24,92; 26,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,04; 26,67</t>
+          <t>26,05; 26,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,93; 27,53</t>
+          <t>26,94; 27,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,32; 27,03</t>
+          <t>26,33; 27,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,67; 29,26</t>
+          <t>26,36; 27,03</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27,2</t>
+          <t>27,15</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,53</t>
+          <t>25,81</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,36</t>
+          <t>26,57</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,23; 26,64</t>
+          <t>26,21; 26,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,74; 27,25</t>
+          <t>26,75; 27,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,7; 27,17</t>
+          <t>26,68; 27,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,93; 27,52</t>
+          <t>26,86; 27,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,78; 25,46</t>
+          <t>24,8; 25,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,48; 26,18</t>
+          <t>25,48; 26,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,04; 25,72</t>
+          <t>25,07; 25,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,61; 30,67</t>
+          <t>25,51; 26,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>25,76; 26,1</t>
+          <t>25,78; 26,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,34; 26,74</t>
+          <t>26,32; 26,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,1; 26,51</t>
+          <t>26,09; 26,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>26,47; 29,38</t>
+          <t>26,37; 26,78</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26,81</t>
+          <t>26,69</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27,06</t>
+          <t>27,18</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,97</t>
+          <t>26,98</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,26; 26,13</t>
+          <t>25,24; 26,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,28; 26,95</t>
+          <t>26,27; 26,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,36; 27,08</t>
+          <t>26,41; 27,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,32; 27,3</t>
+          <t>26,26; 27,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,9; 26,76</t>
+          <t>25,91; 26,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,99; 27,87</t>
+          <t>27,01; 27,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,6; 27,42</t>
+          <t>26,62; 27,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>26,7; 27,39</t>
+          <t>26,87; 27,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,77; 26,37</t>
+          <t>25,75; 26,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,8; 27,4</t>
+          <t>26,84; 27,4</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26,61; 27,17</t>
+          <t>26,64; 27,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,66; 27,27</t>
+          <t>26,75; 27,22</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24,01</t>
+          <t>23,98</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>26,07</t>
+          <t>26,05</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,56</t>
+          <t>25,58</t>
         </is>
       </c>
     </row>
@@ -1416,42 +1416,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,18; 23,87</t>
+          <t>23,19; 23,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23,4; 24,23</t>
+          <t>23,34; 24,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,02; 23,96</t>
+          <t>23,03; 23,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,15; 24,9</t>
+          <t>23,23; 24,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,65; 26,18</t>
+          <t>25,64; 26,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,38; 27,06</t>
+          <t>26,4; 27,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,25; 26,93</t>
+          <t>26,26; 26,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25,74; 26,42</t>
+          <t>25,72; 26,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25,88; 26,44</t>
+          <t>25,86; 26,41</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25,58; 26,18</t>
+          <t>25,61; 26,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25,21; 25,91</t>
+          <t>25,23; 25,9</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26,94</t>
+          <t>26,65</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>26,39</t>
+          <t>25,93</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,66</t>
+          <t>26,28</t>
         </is>
       </c>
     </row>
@@ -1556,47 +1556,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,89; 26,13</t>
+          <t>25,91; 26,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,52; 26,79</t>
+          <t>26,53; 26,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,33; 26,64</t>
+          <t>26,32; 26,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,62; 27,67</t>
+          <t>26,48; 26,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,21; 25,54</t>
+          <t>25,22; 25,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,09; 26,44</t>
+          <t>26,08; 26,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,8; 26,16</t>
+          <t>25,81; 26,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>25,84; 27,87</t>
+          <t>25,79; 26,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,59; 25,79</t>
+          <t>25,59; 25,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26,11; 26,33</t>
+          <t>26,1; 26,33</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,3; 27,6</t>
+          <t>26,17; 26,39</t>
         </is>
       </c>
     </row>
